--- a/Result/profitability/8431.xlsx
+++ b/Result/profitability/8431.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-38.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.275</v>
+        <v>-5.48</v>
       </c>
       <c r="N2" t="n">
-        <v>16.7425</v>
+        <v>14.42625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.28</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.907500000000001</v>
+        <v>-5.19</v>
       </c>
       <c r="N3" t="n">
-        <v>18.5375</v>
+        <v>15.43375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.8625</v>
+        <v>-4.975000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>18.89875</v>
+        <v>18.125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.76375</v>
+        <v>-4.88875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.49375</v>
+        <v>18.605</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -8181,6 +8181,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8431</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>206</v>
+      </c>
+      <c r="D62" t="n">
+        <v>187</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-58</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-28.34%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-70</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-64</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-0.645</v>
+      </c>
+      <c r="N62" t="n">
+        <v>16.6275</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.002157497303128419</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>-7.109999999999999</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.4335365853658537</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
